--- a/reports/rep_all_list_2026-06.xlsx
+++ b/reports/rep_all_list_2026-06.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="539">
   <si>
     <t xml:space="preserve">
         SELECT 
@@ -95,6 +95,57 @@
     <t/>
   </si>
   <si>
+    <t>04.06.2026</t>
+  </si>
+  <si>
+    <t>04.06.2026 08:00</t>
+  </si>
+  <si>
+    <t>04.06.2026 10:10</t>
+  </si>
+  <si>
+    <t>Ахметова Айнур Сериковна</t>
+  </si>
+  <si>
+    <t>Главный специалист по делопроизводству</t>
+  </si>
+  <si>
+    <t>Административный департамент</t>
+  </si>
+  <si>
+    <t xml:space="preserve">у врача маммолог-онколог. по результату скрининга  </t>
+  </si>
+  <si>
+    <t>Турар Аслан Аскарулы</t>
+  </si>
+  <si>
+    <t>Согласовано</t>
+  </si>
+  <si>
+    <t>05.06.2026</t>
+  </si>
+  <si>
+    <t>05.06.2026 14:30</t>
+  </si>
+  <si>
+    <t>05.06.2026 16:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">в больницу, выписали сына после травмы </t>
+  </si>
+  <si>
+    <t>08.06.2026</t>
+  </si>
+  <si>
+    <t>08.06.2026 11:14</t>
+  </si>
+  <si>
+    <t>08.06.2026 12:17</t>
+  </si>
+  <si>
+    <t>В поликлинику  на учёт после операции ребёнка</t>
+  </si>
+  <si>
     <t>01.06.2026 11:00</t>
   </si>
   <si>
@@ -107,16 +158,55 @@
     <t>Внештатный работник</t>
   </si>
   <si>
-    <t>Административный департамент</t>
-  </si>
-  <si>
     <t>Казпочта, отправление документов</t>
   </si>
   <si>
-    <t>Турар Аслан Аскарулы</t>
-  </si>
-  <si>
-    <t>Согласовано</t>
+    <t>03.06.2026</t>
+  </si>
+  <si>
+    <t>03.06.2026 15:50</t>
+  </si>
+  <si>
+    <t>03.06.2026 16:45</t>
+  </si>
+  <si>
+    <t>10.06.2026</t>
+  </si>
+  <si>
+    <t>10.06.2026 10:50</t>
+  </si>
+  <si>
+    <t>10.06.2026 11:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>На согласовании</t>
+  </si>
+  <si>
+    <t>04.06.2026 14:30</t>
+  </si>
+  <si>
+    <t>04.06.2026 18:43</t>
+  </si>
+  <si>
+    <t>Тасболатова Алия Кайратовна</t>
+  </si>
+  <si>
+    <t>Главный специалист</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	По поручению в МТСЗН. Подготовка к совещанию.</t>
+  </si>
+  <si>
+    <t>04.06.2026 18:40</t>
+  </si>
+  <si>
+    <t>Директор</t>
+  </si>
+  <si>
+    <t>Совещание в Министерстве труда. Подготовка.</t>
   </si>
   <si>
     <t>02.06.2026</t>
@@ -143,6 +233,36 @@
     <t>Абдельдинов Ардак Баримжанович</t>
   </si>
   <si>
+    <t>09.06.2026</t>
+  </si>
+  <si>
+    <t>08.06.2026 16:48</t>
+  </si>
+  <si>
+    <t>08.06.2026 17:30</t>
+  </si>
+  <si>
+    <t>Сергебаева Жадра Мухтаркызы</t>
+  </si>
+  <si>
+    <t>Департамент закупок</t>
+  </si>
+  <si>
+    <t>школьное собрание</t>
+  </si>
+  <si>
+    <t>Алибаева Мадина Жасулановна</t>
+  </si>
+  <si>
+    <t>04.06.2026 17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Департамент закупок </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Министерство труда и соц защиты РК </t>
+  </si>
+  <si>
     <t>01.06.2026 14:43</t>
   </si>
   <si>
@@ -155,37 +275,37 @@
     <t>Тест, не согласовывать</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>На согласовании</t>
-  </si>
-  <si>
     <t>01.06.2026 07:56</t>
   </si>
   <si>
+    <t>01.06.2026 13:00</t>
+  </si>
+  <si>
+    <t>Баегизова Дина Асылбековна</t>
+  </si>
+  <si>
+    <t>Департамент контроля качества назначений социальных выплат</t>
+  </si>
+  <si>
+    <t>вход без карты , зашла по карте с Абдыгалиева Айнур</t>
+  </si>
+  <si>
     <t>01.06.2026 08:00</t>
   </si>
   <si>
-    <t>Баегизова Дина Асылбековна</t>
-  </si>
-  <si>
-    <t>Директор</t>
-  </si>
-  <si>
-    <t>Департамент контроля качества назначений социальных выплат</t>
-  </si>
-  <si>
     <t>вход без карты вмести с Абдыгалиева Айнур проектный офис</t>
   </si>
   <si>
     <t>Отказано</t>
   </si>
   <si>
-    <t>01.06.2026 13:00</t>
-  </si>
-  <si>
-    <t>вход без карты , зашла по карте с Абдыгалиева Айнур</t>
+    <t>03.06.2026 11:00</t>
+  </si>
+  <si>
+    <t>03.06.2026 12:45</t>
+  </si>
+  <si>
+    <t>МТСЗН совещание у Шегай ВВ по свур по которым РБ не назначают т.к. участиники</t>
   </si>
   <si>
     <t>02.06.2026 08:00</t>
@@ -197,16 +317,16 @@
     <t>Ертаева Гульмира Бериковна</t>
   </si>
   <si>
-    <t>Главный специалист</t>
-  </si>
-  <si>
     <t>По семейным обстоятельствам</t>
   </si>
   <si>
-    <t>03.06.2026</t>
-  </si>
-  <si>
-    <t>03.06.2026 11:00</t>
+    <t>09.06.2026 14:30</t>
+  </si>
+  <si>
+    <t>09.06.2026 14:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На прием к врачу </t>
   </si>
   <si>
     <t>03.06.2026 13:00</t>
@@ -221,6 +341,15 @@
     <t>Совещание в МТСЗН</t>
   </si>
   <si>
+    <t>05.06.2026 17:00</t>
+  </si>
+  <si>
+    <t>05.06.2026 17:30</t>
+  </si>
+  <si>
+    <t>Прием в поликлинике</t>
+  </si>
+  <si>
     <t>01.06.2026 18:30</t>
   </si>
   <si>
@@ -245,6 +374,51 @@
     <t>В поликлинику</t>
   </si>
   <si>
+    <t>09.06.2026 15:40</t>
+  </si>
+  <si>
+    <t>09.06.2026 15:59</t>
+  </si>
+  <si>
+    <t>Кызаева Жанат Сеилкановна</t>
+  </si>
+  <si>
+    <t>Дәріханаға бардым</t>
+  </si>
+  <si>
+    <t>05.06.2026 08:00</t>
+  </si>
+  <si>
+    <t>05.06.2026 13:00</t>
+  </si>
+  <si>
+    <t>08.06.2026 08:00</t>
+  </si>
+  <si>
+    <t>Алиакпарова Динара Айдаровна</t>
+  </si>
+  <si>
+    <t>Ведущий специалист</t>
+  </si>
+  <si>
+    <t>Департамент по работе с плательщиками</t>
+  </si>
+  <si>
+    <t xml:space="preserve">вход без карты </t>
+  </si>
+  <si>
+    <t>Сагындыкова Шамшия Жолдыбаевна</t>
+  </si>
+  <si>
+    <t>04.06.2026 10:05</t>
+  </si>
+  <si>
+    <t>Байболатқызы Айымгүл</t>
+  </si>
+  <si>
+    <t>была на приеме у врача</t>
+  </si>
+  <si>
     <t>03.06.2026 14:30</t>
   </si>
   <si>
@@ -254,24 +428,72 @@
     <t>Сасбухаев Аскарбек Бобеевич</t>
   </si>
   <si>
-    <t>Департамент по работе с плательщиками</t>
-  </si>
-  <si>
     <t>Поликлиника.</t>
   </si>
   <si>
+    <t>04.06.2026 17:00</t>
+  </si>
+  <si>
+    <t>04.06.2026 09:00</t>
+  </si>
+  <si>
+    <t>Амангелді Әйгерім Амангелдіқызы</t>
+  </si>
+  <si>
+    <t>Департамент по связям с общественностью и международного сотрудничества</t>
+  </si>
+  <si>
+    <t xml:space="preserve">поликлиника </t>
+  </si>
+  <si>
+    <t>08.06.2026 17:00</t>
+  </si>
+  <si>
+    <t>собрание в саду</t>
+  </si>
+  <si>
     <t>01.06.2026 09:09</t>
   </si>
   <si>
     <t>Болатбекова Гульбагила Конырбаевна</t>
   </si>
   <si>
-    <t>Департамент по связям с общественностью и международного сотрудничества</t>
-  </si>
-  <si>
     <t>запись к врачу</t>
   </si>
   <si>
+    <t>Ахмурова Зарина Жоламановна</t>
+  </si>
+  <si>
+    <t>Департамент стратегического развития и методологии</t>
+  </si>
+  <si>
+    <t>Министерство ТСЗН</t>
+  </si>
+  <si>
+    <t>14.06.2026 17:30</t>
+  </si>
+  <si>
+    <t>Апахаева Айдана Асылбековна</t>
+  </si>
+  <si>
+    <t>Контакт центр</t>
+  </si>
+  <si>
+    <t>в министерство с ДАР 14:30-19:00</t>
+  </si>
+  <si>
+    <t>Салимова Гульмира Калеловна</t>
+  </si>
+  <si>
+    <t>09.06.2026 08:05</t>
+  </si>
+  <si>
+    <t>09.06.2026 08:40</t>
+  </si>
+  <si>
+    <t>сдача анализов</t>
+  </si>
+  <si>
     <t>02.06.2026 14:30</t>
   </si>
   <si>
@@ -281,16 +503,40 @@
     <t>Садирбаев Сырымбет Тулкибаевич</t>
   </si>
   <si>
-    <t>Ведущий специалист</t>
-  </si>
-  <si>
-    <t>Контакт центр</t>
-  </si>
-  <si>
     <t>задержался в поликлинике</t>
   </si>
   <si>
-    <t>Салимова Гульмира Калеловна</t>
+    <t>08.06.2026 08:58</t>
+  </si>
+  <si>
+    <t>Сапина Мадина Калдыбаевна</t>
+  </si>
+  <si>
+    <t>Сдача анализов в онко.центр</t>
+  </si>
+  <si>
+    <t>10.06.2026 08:00</t>
+  </si>
+  <si>
+    <t>10.06.2026 09:30</t>
+  </si>
+  <si>
+    <t>За лек. препаратами в онко.центр</t>
+  </si>
+  <si>
+    <t>Ахметкалиева Индира Мухаметрахимовна</t>
+  </si>
+  <si>
+    <t>Главный менеджер</t>
+  </si>
+  <si>
+    <t>Проектный офис</t>
+  </si>
+  <si>
+    <t>Вход без карточки: пропускная карта забыта дома.</t>
+  </si>
+  <si>
+    <t>Абдыгалиева Айнур Дулатовна</t>
   </si>
   <si>
     <t>03.06.2026 09:30</t>
@@ -302,15 +548,9 @@
     <t>Байзакова Арай Становна</t>
   </si>
   <si>
-    <t>Проектный офис</t>
-  </si>
-  <si>
     <t xml:space="preserve">совещание в казэнерджи (ул. Кабанбай батыра 17блок Б) пои вопросам страховой пенсии </t>
   </si>
   <si>
-    <t>Абдыгалиева Айнур Дулатовна</t>
-  </si>
-  <si>
     <t>01.06.2026 12:40</t>
   </si>
   <si>
@@ -326,6 +566,18 @@
     <t xml:space="preserve">спровождение супруга в поликлинику №11 к невропотологу </t>
   </si>
   <si>
+    <t>04.06.2026 10:40</t>
+  </si>
+  <si>
+    <t>сопровождение супруга в офтальмологическое иследование для вкк</t>
+  </si>
+  <si>
+    <t>08.06.2026 15:00</t>
+  </si>
+  <si>
+    <t>сопровождение супруга на прием сосудистому хирургу</t>
+  </si>
+  <si>
     <t>Сарузенов Ғабит Маратұлы</t>
   </si>
   <si>
@@ -335,6 +587,21 @@
     <t>Вход без карты</t>
   </si>
   <si>
+    <t>08.06.2026 14:30</t>
+  </si>
+  <si>
+    <t>08.06.2026 15:45</t>
+  </si>
+  <si>
+    <t>Жангарина Динара Борисовна</t>
+  </si>
+  <si>
+    <t>Служба риск менеджмента</t>
+  </si>
+  <si>
+    <t>посещение ЧЛХ врача поликлиника 2</t>
+  </si>
+  <si>
     <t>03.06.2026 09:45</t>
   </si>
   <si>
@@ -353,6 +620,18 @@
     <t>поход к врачу</t>
   </si>
   <si>
+    <t>Джусупбекова Алия Асылхановна</t>
+  </si>
+  <si>
+    <t>Управление бухгалтерского учета и отчетности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вход без карты </t>
+  </si>
+  <si>
+    <t>Елеуова Гульмира Саветовна</t>
+  </si>
+  <si>
     <t>02.06.2026 15:55</t>
   </si>
   <si>
@@ -371,6 +650,81 @@
     <t>Сабырова Айнагуль Мирзабековна</t>
   </si>
   <si>
+    <t>04.06.2026 18:00</t>
+  </si>
+  <si>
+    <t>Заседание по Тимеевой</t>
+  </si>
+  <si>
+    <t>08.06.2026 08:30</t>
+  </si>
+  <si>
+    <t>08.06.2026 09:40</t>
+  </si>
+  <si>
+    <t>Нуршарипова Айгерим Талгатовна</t>
+  </si>
+  <si>
+    <t>Суд по Тимеевой Э.</t>
+  </si>
+  <si>
+    <t>05.06.2026 14:15</t>
+  </si>
+  <si>
+    <t>05.06.2026 16:35</t>
+  </si>
+  <si>
+    <t>Встреча с населением, вице-министром Шегай В.В.</t>
+  </si>
+  <si>
+    <t>Суд по Бағдат Э.</t>
+  </si>
+  <si>
+    <t>05.06.2026 16:30</t>
+  </si>
+  <si>
+    <t>Встреча вице-министра с населением в "Дом дружбы"</t>
+  </si>
+  <si>
+    <t>Темірхан Әлия Булатқызы</t>
+  </si>
+  <si>
+    <t>Специалист</t>
+  </si>
+  <si>
+    <t>Встреча с населением вице министра Шегай В.В.</t>
+  </si>
+  <si>
+    <t>09.06.2026 09:50</t>
+  </si>
+  <si>
+    <t>09.06.2026 14:08</t>
+  </si>
+  <si>
+    <t>Абдрахимов Ерканат Айдарханович</t>
+  </si>
+  <si>
+    <t>Заместитель директора</t>
+  </si>
+  <si>
+    <t>Филиал по Алматинской области</t>
+  </si>
+  <si>
+    <t>Алматы облысы бойынша «Экономикалық тергеп тексеру департаментінің» сұранысы бойынша сот сараптамасын жүргізуге байланысты қылмыстық іс материалдары бойынша ӘТжб құжаттары қағаз нұсқада жеткізілді.</t>
+  </si>
+  <si>
+    <t>Аманбаев Ерлан Оралбекович</t>
+  </si>
+  <si>
+    <t>03.06.2026 12:15</t>
+  </si>
+  <si>
+    <t>03.06.2026 18:29</t>
+  </si>
+  <si>
+    <t>выезд в ДЭР по Алматинской области (г.Алматы)</t>
+  </si>
+  <si>
     <t>01.06.2026 14:00</t>
   </si>
   <si>
@@ -380,15 +734,9 @@
     <t>Байзакова Эльзат Канабековна</t>
   </si>
   <si>
-    <t>Филиал по Алматинской области</t>
-  </si>
-  <si>
     <t>была на Казпочте.</t>
   </si>
   <si>
-    <t>Аманбаев Ерлан Оралбекович</t>
-  </si>
-  <si>
     <t>03.06.2026 14:00</t>
   </si>
   <si>
@@ -404,9 +752,6 @@
     <t>Аманбаев Сабит Болысулы</t>
   </si>
   <si>
-    <t>Специалист</t>
-  </si>
-  <si>
     <t>Филиал по Атырауской области</t>
   </si>
   <si>
@@ -416,6 +761,15 @@
     <t>Бағытов Райымбек Еркінұлы</t>
   </si>
   <si>
+    <t>08.06.2026 10:40</t>
+  </si>
+  <si>
+    <t>Бисенов Ербол Жеткеншекұлы</t>
+  </si>
+  <si>
+    <t>Запись к врачу</t>
+  </si>
+  <si>
     <t>02.06.2026 09:00</t>
   </si>
   <si>
@@ -428,18 +782,36 @@
     <t>судебный процесс по Б.Ахметовой</t>
   </si>
   <si>
+    <t>10.06.2026 11:50</t>
+  </si>
+  <si>
+    <t>10.06.2026 14:30</t>
+  </si>
+  <si>
+    <t>ИРР КТЖ перевозки</t>
+  </si>
+  <si>
+    <t>Жумажанова Анар Сайлауовна</t>
+  </si>
+  <si>
+    <t>Филиал по Восточно-Казахстанской области</t>
+  </si>
+  <si>
+    <t>выезд в Казпочту</t>
+  </si>
+  <si>
+    <t>Кыстаубаев Нурлан Толеубекович</t>
+  </si>
+  <si>
     <t>02.06.2026 17:16</t>
   </si>
   <si>
-    <t>Кыстаубаев Нурлан Толеубекович</t>
-  </si>
-  <si>
-    <t>Филиал по Восточно-Казахстанской области</t>
-  </si>
-  <si>
     <t>в уголовном суде по возврату ОПВ с ЕНПФ в ГФСС</t>
   </si>
   <si>
+    <t>05.06.2026 16:10</t>
+  </si>
+  <si>
     <t>Нурсултанова Айнур Нурлановна</t>
   </si>
   <si>
@@ -449,6 +821,18 @@
     <t>в уголовном суде по ОПВ</t>
   </si>
   <si>
+    <t>в суде по уголовному делу</t>
+  </si>
+  <si>
+    <t>08.06.2026 11:00</t>
+  </si>
+  <si>
+    <t>08.06.2026 13:00</t>
+  </si>
+  <si>
+    <t>Уалиев Ахат Амангельдинович</t>
+  </si>
+  <si>
     <t>02.06.2026 16:53</t>
   </si>
   <si>
@@ -464,6 +848,21 @@
     <t>ходила на почту</t>
   </si>
   <si>
+    <t>Гримова Елена Николаевна</t>
+  </si>
+  <si>
+    <t>04.06.2026 15:08</t>
+  </si>
+  <si>
+    <t>04.06.2026 16:36</t>
+  </si>
+  <si>
+    <t>05.06.2026 16:44</t>
+  </si>
+  <si>
+    <t>05.06.2026 17:23</t>
+  </si>
+  <si>
     <t>03.06.2026 08:15</t>
   </si>
   <si>
@@ -482,6 +881,15 @@
     <t>Юдина Наталья Павловна</t>
   </si>
   <si>
+    <t>04.06.2026 08:53</t>
+  </si>
+  <si>
+    <t>04.06.2026 09:24</t>
+  </si>
+  <si>
+    <t>09.06.2026 14:49</t>
+  </si>
+  <si>
     <t>03.06.2026 09:22</t>
   </si>
   <si>
@@ -491,6 +899,30 @@
     <t>Тематическая учеба у директора</t>
   </si>
   <si>
+    <t>08.06.2026 14:38</t>
+  </si>
+  <si>
+    <t>08.06.2026 15:04</t>
+  </si>
+  <si>
+    <t>Отправка писем через АО Казпочта</t>
+  </si>
+  <si>
+    <t>08.06.2026 12:37</t>
+  </si>
+  <si>
+    <t>Приём к врачу</t>
+  </si>
+  <si>
+    <t>10.06.2026 09:45</t>
+  </si>
+  <si>
+    <t>10.06.2026 10:58</t>
+  </si>
+  <si>
+    <t>Мероприятие День открытых дверей</t>
+  </si>
+  <si>
     <t>01.06.2026 14:30</t>
   </si>
   <si>
@@ -518,18 +950,18 @@
     <t>Поликлиника мед. процедуры</t>
   </si>
   <si>
+    <t>03.06.2026 09:00</t>
+  </si>
+  <si>
+    <t>совещание у директора</t>
+  </si>
+  <si>
     <t>03.06.2026 09:01</t>
   </si>
   <si>
     <t>03.06.2026 10:20</t>
   </si>
   <si>
-    <t>03.06.2026 09:00</t>
-  </si>
-  <si>
-    <t>совещание у директора</t>
-  </si>
-  <si>
     <t>Муканова Асель Абаевна</t>
   </si>
   <si>
@@ -542,6 +974,15 @@
     <t>Тематическая учеба в кабинете у директора</t>
   </si>
   <si>
+    <t>10.06.2026 09:47</t>
+  </si>
+  <si>
+    <t>10.06.2026 12:07</t>
+  </si>
+  <si>
+    <t>Проведение Дня открытых дверей в НАО «Государственная корпорация «Правительство для граждан» по Костанайской области</t>
+  </si>
+  <si>
     <t>03.06.2026 10:00</t>
   </si>
   <si>
@@ -554,6 +995,15 @@
     <t>Утегенова Гаухар Сабитовна</t>
   </si>
   <si>
+    <t>09.06.2026 10:50</t>
+  </si>
+  <si>
+    <t>09.06.2026 11:40</t>
+  </si>
+  <si>
+    <t>выход в акимат г.Костанай- подготовка к заседанию 3-х сторонней комиссии</t>
+  </si>
+  <si>
     <t>Денеева Гулсим Жумагалиевна</t>
   </si>
   <si>
@@ -572,6 +1022,18 @@
     <t>03.06.2026 08:50</t>
   </si>
   <si>
+    <t>04.06.2026 08:50</t>
+  </si>
+  <si>
+    <t>Академияда біліктілікті арттыру оқуда. Ақпараттық түсіндіру жұмысы</t>
+  </si>
+  <si>
+    <t>05.06.2026 08:50</t>
+  </si>
+  <si>
+    <t>05.06.2026 12:15</t>
+  </si>
+  <si>
     <t>01.06.2026 09:00</t>
   </si>
   <si>
@@ -587,6 +1049,18 @@
     <t>Мемлекеттік басқару академиясында оқуда және мектепте болдым</t>
   </si>
   <si>
+    <t>04.06.2026 13:30</t>
+  </si>
+  <si>
+    <t>09.06.2026 12:00</t>
+  </si>
+  <si>
+    <t>09.06.2026 13:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">была в поликлинике </t>
+  </si>
+  <si>
     <t>01.06.2026 15:20</t>
   </si>
   <si>
@@ -599,6 +1073,18 @@
     <t>03.06.2026 15:15</t>
   </si>
   <si>
+    <t>04.06.2026 14:55</t>
+  </si>
+  <si>
+    <t>04.06.2026 15:35</t>
+  </si>
+  <si>
+    <t>09.06.2026 15:15</t>
+  </si>
+  <si>
+    <t>РП ЧСИ-(исполнительные листы)</t>
+  </si>
+  <si>
     <t>Кожамуратов Сеитжан Назарович</t>
   </si>
   <si>
@@ -623,6 +1109,27 @@
     <t xml:space="preserve">Прием у Председателей обл суда и СМАС </t>
   </si>
   <si>
+    <t>04.06.2026 14:45</t>
+  </si>
+  <si>
+    <t>04.06.2026 17:05</t>
+  </si>
+  <si>
+    <t>гор суд по уг делу 054</t>
+  </si>
+  <si>
+    <t>08.06.2026 14:50</t>
+  </si>
+  <si>
+    <t>08.06.2026 15:35</t>
+  </si>
+  <si>
+    <t>09.06.2026 14:45</t>
+  </si>
+  <si>
+    <t>09.06.2026 17:10</t>
+  </si>
+  <si>
     <t>03.06.2026 10:45</t>
   </si>
   <si>
@@ -632,6 +1139,18 @@
     <t>участие в уголовном процессе</t>
   </si>
   <si>
+    <t>04.06.2026 15:00</t>
+  </si>
+  <si>
+    <t>08.06.2026 14:45</t>
+  </si>
+  <si>
+    <t>08.06.2026 15:30</t>
+  </si>
+  <si>
+    <t>09.06.2026 17:00</t>
+  </si>
+  <si>
     <t>01.06.2026 15:50</t>
   </si>
   <si>
@@ -644,6 +1163,12 @@
     <t xml:space="preserve">выезд на почту </t>
   </si>
   <si>
+    <t>04.06.2026 11:35</t>
+  </si>
+  <si>
+    <t>04.06.2026 12:10</t>
+  </si>
+  <si>
     <t>03.06.2026 09:20</t>
   </si>
   <si>
@@ -656,6 +1181,45 @@
     <t>встреча с труд коллективом трамвайного управления</t>
   </si>
   <si>
+    <t>05.06.2026 15:00</t>
+  </si>
+  <si>
+    <t>проведение мероприятия ДОД</t>
+  </si>
+  <si>
+    <t>09.06.2026 11:50</t>
+  </si>
+  <si>
+    <t>09.06.2026 13:00</t>
+  </si>
+  <si>
+    <t>проведение ИРР в Виамедис Павлодар</t>
+  </si>
+  <si>
+    <t>05.06.2026 16:00</t>
+  </si>
+  <si>
+    <t>05.06.2026 17:49</t>
+  </si>
+  <si>
+    <t>Суюшпаева Жибек Шорановна</t>
+  </si>
+  <si>
+    <t>Помогать в проведении мероприятия День открытых дверей, встречать участвующих, снимать на фото видео и т.д.</t>
+  </si>
+  <si>
+    <t>05.06.2026 14:50</t>
+  </si>
+  <si>
+    <t>05.06.2026 15:50</t>
+  </si>
+  <si>
+    <t>Хасенова Замира Каирбековна</t>
+  </si>
+  <si>
+    <t>казпочта. отправка писем</t>
+  </si>
+  <si>
     <t>01.06.2026 10:20</t>
   </si>
   <si>
@@ -680,6 +1244,15 @@
     <t>на приеме у стоматолога</t>
   </si>
   <si>
+    <t>05.06.2026 10:35</t>
+  </si>
+  <si>
+    <t>05.06.2026 12:20</t>
+  </si>
+  <si>
+    <t>участие на заседание рабочей группы по усилению взаимодействия с уполномоченными органами и увеличению поступлений в бюджет г. Петропавловска на 2026 год</t>
+  </si>
+  <si>
     <t>03.06.2026 14:58</t>
   </si>
   <si>
@@ -713,6 +1286,24 @@
     <t>оформление в детский сад</t>
   </si>
   <si>
+    <t>08.06.2026 09:30</t>
+  </si>
+  <si>
+    <t>День открытых дверей в ТРЦ Достык мол</t>
+  </si>
+  <si>
+    <t>04.06.2026 16:50</t>
+  </si>
+  <si>
+    <t>Муканова Алия Мейрамовна</t>
+  </si>
+  <si>
+    <t>с ребенком к стоматологу</t>
+  </si>
+  <si>
+    <t>05.06.2026 16:50</t>
+  </si>
+  <si>
     <t>01.06.2026 09:50</t>
   </si>
   <si>
@@ -731,6 +1322,24 @@
     <t>В Казпочту для отправки корреспонденции</t>
   </si>
   <si>
+    <t>04.06.2026 16:30</t>
+  </si>
+  <si>
+    <t>05.06.2026 09:30</t>
+  </si>
+  <si>
+    <t>В поликлинике с ребенком (профосмотр)</t>
+  </si>
+  <si>
+    <t>"День открытых дверей" на площадке ТРЦ «Dostyq mall»</t>
+  </si>
+  <si>
+    <t>09.06.2026 16:20</t>
+  </si>
+  <si>
+    <t>09.06.2026 17:30</t>
+  </si>
+  <si>
     <t>Ілес Ғалымжан Бауыржанұлы</t>
   </si>
   <si>
@@ -755,6 +1364,30 @@
     <t>почтаға бардым</t>
   </si>
   <si>
+    <t>04.06.2026 15:10</t>
+  </si>
+  <si>
+    <t>Отбасылық жағдай</t>
+  </si>
+  <si>
+    <t>Хакимова Айнур Адильбековна</t>
+  </si>
+  <si>
+    <t>08.06.2026 16:30</t>
+  </si>
+  <si>
+    <t>Жунусова Жанетта Бакытжановна</t>
+  </si>
+  <si>
+    <t>проведение разнеснительных работ по ирр</t>
+  </si>
+  <si>
+    <t>Қамбарова Гүлсім Нұрланқызы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Дания МЕД түсіндірме жұмыстарын жүргізу. </t>
+  </si>
+  <si>
     <t>03.06.2026 16:00</t>
   </si>
   <si>
@@ -770,6 +1403,9 @@
     <t>ауэзов суд исп листы</t>
   </si>
   <si>
+    <t>Сагинбекова Лаззат Суанбаевна</t>
+  </si>
+  <si>
     <t>02.06.2026 14:59</t>
   </si>
   <si>
@@ -779,7 +1415,13 @@
     <t>ИРР в Общеобразовательная школа № 76</t>
   </si>
   <si>
-    <t>Сагинбекова Лаззат Суанбаевна</t>
+    <t>10.06.2026 12:05</t>
+  </si>
+  <si>
+    <t>10.06.2026 13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">участие в судебном процессе Мельниковой </t>
   </si>
   <si>
     <t>Тленчиева Жулдыз Алибековна</t>
@@ -788,6 +1430,27 @@
     <t>ИРР ТОО "Меридиан Строй"</t>
   </si>
   <si>
+    <t>04.06.2026 12:00</t>
+  </si>
+  <si>
+    <t>04.06.2026 13:00</t>
+  </si>
+  <si>
+    <t>Касенова Айжан Сарсенбиевна</t>
+  </si>
+  <si>
+    <t>Филиал по г.Астана</t>
+  </si>
+  <si>
+    <t>банк Берекебанк</t>
+  </si>
+  <si>
+    <t>09.06.2026 16:00</t>
+  </si>
+  <si>
+    <t>Центральный аппарат</t>
+  </si>
+  <si>
     <t>02.06.2026 15:50</t>
   </si>
   <si>
@@ -797,36 +1460,114 @@
     <t>Мусина Алтын Бауыржановна</t>
   </si>
   <si>
-    <t>Филиал по г.Астана</t>
-  </si>
-  <si>
     <t>Ушла на Каз почту</t>
   </si>
   <si>
-    <t>Касенова Айжан Сарсенбиевна</t>
+    <t>04.06.2026 09:30</t>
+  </si>
+  <si>
+    <t>04.06.2026 10:50</t>
+  </si>
+  <si>
+    <t>Ушла в ЦА АО ГФСС</t>
+  </si>
+  <si>
+    <t>05.06.2026 11:00</t>
+  </si>
+  <si>
+    <t>Ахметова Сауле Куттыбековна</t>
+  </si>
+  <si>
+    <t>Филиал по г.Шымкент</t>
+  </si>
+  <si>
+    <t>посещение собрания в школе</t>
+  </si>
+  <si>
+    <t>Тиллабеков Досбол Алибекович</t>
+  </si>
+  <si>
+    <t>04.06.2026 11:30</t>
+  </si>
+  <si>
+    <t>Гильманова Асем Есеновна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">выезд  на почту </t>
+  </si>
+  <si>
+    <t>04.06.2026 16:10</t>
+  </si>
+  <si>
+    <t>Есенбаева Раушан Берикбосынова</t>
+  </si>
+  <si>
+    <t>посещение поликлиники по состоянию здоровья</t>
+  </si>
+  <si>
+    <t>Конырбаев Дастан Серикбаевич</t>
+  </si>
+  <si>
+    <t>Для сдачи анализа в центр крови. Донор крови</t>
+  </si>
+  <si>
+    <t>08.06.2026 10:00</t>
+  </si>
+  <si>
+    <t>08.06.2026 11:30</t>
+  </si>
+  <si>
+    <t>Информационно-разьяснительная работа</t>
   </si>
   <si>
     <t>03.06.2026 16:30</t>
   </si>
   <si>
-    <t>Тиллабеков Досбол Алибекович</t>
-  </si>
-  <si>
-    <t>Филиал по г.Шымкент</t>
-  </si>
-  <si>
     <t xml:space="preserve">в ДЭР по уг. делу </t>
   </si>
   <si>
+    <t>Тогисбаева Гульмира Миятбековна</t>
+  </si>
+  <si>
+    <t>Информационная разьяснительная работа</t>
+  </si>
+  <si>
+    <t>08.06.2026 12:30</t>
+  </si>
+  <si>
+    <t>05.06.2026 10:00</t>
+  </si>
+  <si>
+    <t>05.06.2026 12:30</t>
+  </si>
+  <si>
+    <t>Изатова Айжан Ериковна</t>
+  </si>
+  <si>
+    <t>Филиал по области Жетісу</t>
+  </si>
+  <si>
+    <t>выезд в АО Казпочта для участия в мероприятии День открытых дверей</t>
+  </si>
+  <si>
+    <t>Боранбек Эльмира</t>
+  </si>
+  <si>
+    <t>05.06.2026 11:15</t>
+  </si>
+  <si>
+    <t>Кабдрахманов Бауыржан Серикович</t>
+  </si>
+  <si>
+    <t>День открытых дверей</t>
+  </si>
+  <si>
     <t>03.06.2026 15:10</t>
   </si>
   <si>
     <t>Маратұлы Қуаныш</t>
   </si>
   <si>
-    <t>Филиал по области Жетісу</t>
-  </si>
-  <si>
     <t>Выезд в Казпочту.</t>
   </si>
   <si>
@@ -848,6 +1589,36 @@
     <t>Корнеевец Валерия Андреевна</t>
   </si>
   <si>
+    <t>08.06.2026 17:10</t>
+  </si>
+  <si>
+    <t>08.06.2026 18:30</t>
+  </si>
+  <si>
+    <t>Судебный процесс</t>
+  </si>
+  <si>
+    <t>09.06.2026 16:10</t>
+  </si>
+  <si>
+    <t>09.06.2026 18:00</t>
+  </si>
+  <si>
+    <t>Передача исполнительных листов ЧСИ</t>
+  </si>
+  <si>
+    <t>05.06.2026 10:30</t>
+  </si>
+  <si>
+    <t>05.06.2026 14:21</t>
+  </si>
+  <si>
+    <t>Сұлтанова Дина Қанатқызы</t>
+  </si>
+  <si>
+    <t>проведение ИРР</t>
+  </si>
+  <si>
     <t>03.06.2026 15:55</t>
   </si>
   <si>
@@ -872,7 +1643,7 @@
     <t>TIMEOFF</t>
   </si>
   <si>
-    <t>Дата формирования: 03.06.2026 (16:45:02)</t>
+    <t>Дата формирования: 10.06.2026 (12:32:25)</t>
   </si>
 </sst>
 </file>
@@ -1295,7 +2066,7 @@
         <v>1</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>280</v>
+        <v>537</v>
       </c>
     </row>
     <row r="2">
@@ -1303,7 +2074,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>281</v>
+        <v>538</v>
       </c>
     </row>
     <row r="3">
@@ -1375,31 +2146,31 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -1407,31 +2178,31 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>36</v>
-      </c>
       <c r="I6" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -1439,31 +2210,31 @@
         <v>4</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="I7" s="5" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -1474,28 +2245,28 @@
         <v>13</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -1503,31 +2274,31 @@
         <v>6</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -1535,31 +2306,31 @@
         <v>7</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -1567,31 +2338,31 @@
         <v>8</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -1599,31 +2370,31 @@
         <v>9</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -1631,31 +2402,31 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>71</v>
-      </c>
       <c r="I13" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -1663,31 +2434,31 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="H14" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="I14" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="J14" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -1695,31 +2466,31 @@
         <v>12</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="I15" s="5" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -1727,31 +2498,31 @@
         <v>13</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C16" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>86</v>
-      </c>
       <c r="I16" s="5" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1759,31 +2530,31 @@
         <v>14</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>56</v>
-      </c>
       <c r="G17" s="5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
@@ -1794,28 +2565,28 @@
         <v>13</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
@@ -1823,31 +2594,31 @@
         <v>16</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>56</v>
-      </c>
       <c r="G19" s="5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -1855,31 +2626,31 @@
         <v>17</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -1887,31 +2658,31 @@
         <v>18</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
@@ -1919,31 +2690,31 @@
         <v>19</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -1951,31 +2722,31 @@
         <v>20</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -1983,31 +2754,31 @@
         <v>21</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -2015,31 +2786,31 @@
         <v>22</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -2047,31 +2818,31 @@
         <v>23</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -2079,31 +2850,31 @@
         <v>24</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
@@ -2111,31 +2882,31 @@
         <v>25</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>70</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
@@ -2143,31 +2914,31 @@
         <v>26</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
@@ -2175,31 +2946,31 @@
         <v>27</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>70</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="F30" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H30" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="I30" s="5" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
@@ -2207,31 +2978,31 @@
         <v>28</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
@@ -2239,31 +3010,31 @@
         <v>29</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -2271,31 +3042,31 @@
         <v>30</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>145</v>
+        <v>23</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34">
@@ -2303,31 +3074,31 @@
         <v>31</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35">
@@ -2335,31 +3106,31 @@
         <v>32</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36">
@@ -2367,31 +3138,31 @@
         <v>33</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>159</v>
+        <v>52</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37">
@@ -2399,31 +3170,31 @@
         <v>34</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>163</v>
+        <v>52</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>42</v>
+        <v>151</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
@@ -2431,31 +3202,31 @@
         <v>35</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>42</v>
+        <v>151</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39">
@@ -2463,31 +3234,31 @@
         <v>36</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
@@ -2495,31 +3266,31 @@
         <v>37</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>42</v>
+        <v>151</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
@@ -2527,31 +3298,31 @@
         <v>38</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42">
@@ -2559,31 +3330,31 @@
         <v>39</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>146</v>
+        <v>70</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43">
@@ -2591,31 +3362,31 @@
         <v>40</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
@@ -2623,31 +3394,31 @@
         <v>41</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>178</v>
+        <v>87</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>175</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G44" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H44" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="H44" s="5" t="s">
-        <v>177</v>
-      </c>
       <c r="I44" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45">
@@ -2655,31 +3426,31 @@
         <v>42</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>175</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
@@ -2687,31 +3458,31 @@
         <v>43</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>181</v>
+        <v>23</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J46" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47">
@@ -2719,31 +3490,31 @@
         <v>44</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>184</v>
+        <v>70</v>
       </c>
       <c r="E47" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H47" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="F47" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>185</v>
-      </c>
       <c r="I47" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="J47" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
@@ -2751,31 +3522,31 @@
         <v>45</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>180</v>
+        <v>93</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="H48" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="I48" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="I48" s="5" t="s">
-        <v>175</v>
-      </c>
       <c r="J48" s="5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49">
@@ -2783,31 +3554,31 @@
         <v>46</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50">
@@ -2815,31 +3586,31 @@
         <v>47</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>72</v>
+        <v>191</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>25</v>
+        <v>194</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="J50" s="5" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51">
@@ -2847,31 +3618,31 @@
         <v>48</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52">
@@ -2879,31 +3650,31 @@
         <v>49</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>47</v>
+        <v>203</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53">
@@ -2911,31 +3682,31 @@
         <v>50</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>47</v>
+        <v>203</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
@@ -2943,31 +3714,31 @@
         <v>51</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>110</v>
+        <v>203</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>190</v>
+        <v>50</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55">
@@ -2975,31 +3746,31 @@
         <v>52</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>201</v>
+        <v>134</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56">
@@ -3007,31 +3778,31 @@
         <v>53</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>60</v>
+        <v>214</v>
       </c>
       <c r="E56" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="I56" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="F56" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="H56" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="I56" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="J56" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57">
@@ -3039,31 +3810,31 @@
         <v>54</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>206</v>
+        <v>50</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58">
@@ -3071,31 +3842,31 @@
         <v>55</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>209</v>
+        <v>32</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="J58" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59">
@@ -3103,31 +3874,31 @@
         <v>56</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C59" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>215</v>
-      </c>
       <c r="E59" s="5" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="J59" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60">
@@ -3135,31 +3906,31 @@
         <v>57</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>72</v>
+        <v>222</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61">
@@ -3167,31 +3938,31 @@
         <v>58</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>223</v>
+        <v>58</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="J61" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62">
@@ -3202,28 +3973,28 @@
         <v>13</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>45</v>
+        <v>232</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E62" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="F62" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>212</v>
-      </c>
       <c r="H62" s="5" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="J62" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
@@ -3231,31 +4002,31 @@
         <v>60</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>45</v>
+        <v>236</v>
       </c>
       <c r="D63" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="I63" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="I63" s="5" t="s">
-        <v>211</v>
-      </c>
       <c r="J63" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -3266,28 +4037,28 @@
         <v>13</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>123</v>
+        <v>239</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>25</v>
+        <v>220</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>212</v>
+        <v>241</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="I64" s="5" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="J64" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65">
@@ -3295,31 +4066,31 @@
         <v>62</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>22</v>
+        <v>244</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>56</v>
+        <v>220</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66">
@@ -3327,31 +4098,31 @@
         <v>63</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>25</v>
+        <v>203</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="I66" s="5" t="s">
-        <v>42</v>
+        <v>243</v>
       </c>
       <c r="J66" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67">
@@ -3359,31 +4130,31 @@
         <v>64</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>110</v>
+        <v>203</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="I67" s="5" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68">
@@ -3391,31 +4162,31 @@
         <v>65</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>247</v>
+        <v>104</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="I68" s="5" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69">
@@ -3423,31 +4194,31 @@
         <v>66</v>
       </c>
       <c r="B69" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="F69" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C69" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>125</v>
-      </c>
       <c r="G69" s="5" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="I69" s="5" t="s">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="J69" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70">
@@ -3455,31 +4226,31 @@
         <v>67</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>253</v>
+        <v>170</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>254</v>
+        <v>113</v>
       </c>
       <c r="E70" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G70" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="F70" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G70" s="5" t="s">
-        <v>256</v>
-      </c>
       <c r="H70" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="I70" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="I70" s="5" t="s">
-        <v>258</v>
-      </c>
       <c r="J70" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71">
@@ -3487,31 +4258,31 @@
         <v>68</v>
       </c>
       <c r="B71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="F71" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C71" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D71" s="6" t="s">
+      <c r="G71" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="H71" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>262</v>
-      </c>
       <c r="I71" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72">
@@ -3519,31 +4290,31 @@
         <v>69</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>25</v>
+        <v>203</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="J72" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73">
@@ -3551,31 +4322,31 @@
         <v>70</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>267</v>
+        <v>170</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>268</v>
+        <v>113</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>110</v>
+        <v>203</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="I73" s="5" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="J73" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
@@ -3583,31 +4354,31 @@
         <v>71</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>72</v>
+        <v>260</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>273</v>
+        <v>105</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>25</v>
+        <v>203</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="J74" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75">
@@ -3615,31 +4386,3359 @@
         <v>72</v>
       </c>
       <c r="B75" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="J75" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11">
+        <v>73</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11">
+        <v>74</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="J77" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11">
+        <v>75</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="J78" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11">
+        <v>76</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11">
+        <v>77</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11">
+        <v>78</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H81" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J81" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11">
+        <v>79</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J82" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11">
+        <v>80</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J83" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11">
+        <v>81</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J84" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11">
+        <v>82</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="11">
+        <v>83</v>
+      </c>
+      <c r="B86" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C75" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D75" s="6" t="s">
+      <c r="C86" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J86" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="11">
+        <v>84</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J87" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="11">
+        <v>85</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J88" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11">
+        <v>86</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J89" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="11">
+        <v>87</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J90" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="11">
+        <v>88</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J91" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="11">
+        <v>89</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="11">
+        <v>90</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H93" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J93" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="11">
+        <v>91</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J94" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="11">
+        <v>92</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J95" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="11">
+        <v>93</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J96" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="11">
+        <v>94</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="H97" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="I97" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="J97" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="11">
+        <v>95</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="J98" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="11">
+        <v>96</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H99" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="J99" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="11">
+        <v>97</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H100" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="J100" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11">
+        <v>98</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H101" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="I101" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="J101" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="11">
+        <v>99</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H102" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="I102" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="J102" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11">
+        <v>100</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H103" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="I103" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="J103" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11">
+        <v>101</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H104" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="I104" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="J104" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11">
+        <v>102</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="I105" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="J105" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11">
+        <v>103</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H106" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="I106" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="J106" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11">
+        <v>104</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H107" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="I107" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="J107" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11">
+        <v>105</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G108" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H108" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J108" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="11">
+        <v>106</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H109" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="I109" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="J109" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11">
+        <v>107</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H110" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="11">
+        <v>108</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H111" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="J111" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="11">
+        <v>109</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H112" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J112" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="11">
+        <v>110</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H113" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="I113" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J113" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="11">
+        <v>111</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G114" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H114" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="I114" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J114" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="11">
+        <v>112</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H115" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="I115" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J115" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="11">
+        <v>113</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H116" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="I116" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J116" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="11">
+        <v>114</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H117" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="I117" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J117" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="11">
+        <v>115</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H118" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="I118" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J118" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="11">
+        <v>116</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H119" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="I119" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J119" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="11">
+        <v>117</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H120" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="I120" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J120" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="11">
+        <v>118</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H121" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="I121" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J121" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="11">
+        <v>119</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H122" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="I122" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J122" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="11">
+        <v>120</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H123" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="I123" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J123" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="11">
+        <v>121</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H124" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="I124" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="J124" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="11">
+        <v>122</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G125" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="H125" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="I125" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J125" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="11">
+        <v>123</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="H126" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="I126" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="J126" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="11">
+        <v>124</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G127" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="H127" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="I127" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J127" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="11">
+        <v>125</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G128" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="H128" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="I128" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J128" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11">
+        <v>126</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="H129" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="I129" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="J129" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11">
+        <v>127</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G130" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="H130" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="I130" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="J130" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11">
+        <v>128</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H131" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="I131" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J131" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="11">
+        <v>129</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H132" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="I132" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J132" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="11">
+        <v>130</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H133" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="I133" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J133" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="11">
+        <v>131</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H134" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="I134" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J134" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11">
+        <v>132</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="G135" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H135" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="I135" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J135" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="11">
+        <v>133</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H136" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="I136" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J136" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="11">
+        <v>134</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H137" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="I137" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J137" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="11">
+        <v>135</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G138" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H138" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="I138" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J138" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11">
+        <v>136</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H139" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="I139" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J139" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11">
+        <v>137</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H140" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="I140" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J140" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="11">
+        <v>138</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H141" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="I141" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J141" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="11">
+        <v>139</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H142" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="I142" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J142" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11">
+        <v>140</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H143" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="I143" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J143" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="11">
+        <v>141</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H144" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="I144" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J144" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="11">
+        <v>142</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H145" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="I145" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="J145" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="11">
+        <v>143</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="H146" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="I146" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="J146" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="11">
+        <v>144</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="H147" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="I147" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="J147" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="11">
+        <v>145</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G148" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="H148" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="I148" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="J148" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="11">
+        <v>146</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="H149" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="I149" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="J149" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="11">
+        <v>147</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="H150" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="I150" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="J150" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="11">
+        <v>148</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G151" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="H151" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="I151" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="J151" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="11">
+        <v>149</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="H152" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="I152" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="J152" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="11">
+        <v>150</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G153" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="H153" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="I153" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="J153" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="11">
+        <v>151</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="E154" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="H154" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="I154" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J154" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="11">
+        <v>152</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="E155" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G155" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="H155" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="I155" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="J155" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="11">
+        <v>153</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G156" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="H156" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="I156" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="J156" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="11">
+        <v>154</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="E157" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="H157" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="I157" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="J157" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="11">
+        <v>155</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="H158" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I158" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="J158" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="11">
+        <v>156</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="H159" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="I159" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="J159" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="11">
+        <v>157</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G160" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="H160" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="I160" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="J160" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="11">
+        <v>158</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E161" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="F161" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E75" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="I75" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="J75" s="5" t="s">
-        <v>29</v>
+      <c r="G161" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="H161" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="I161" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="J161" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="11">
+        <v>159</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G162" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="H162" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="I162" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="J162" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="11">
+        <v>160</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="H163" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="I163" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="J163" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="11">
+        <v>161</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E164" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G164" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="H164" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="I164" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="J164" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="11">
+        <v>162</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E165" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="H165" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="I165" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="J165" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="11">
+        <v>163</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="H166" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="I166" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="J166" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="11">
+        <v>164</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G167" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="H167" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="I167" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="J167" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="11">
+        <v>165</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G168" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="H168" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="I168" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="J168" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="11">
+        <v>166</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="H169" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="I169" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="J169" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="11">
+        <v>167</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="H170" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="I170" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="J170" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="11">
+        <v>168</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G171" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="H171" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="I171" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="J171" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="11">
+        <v>169</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="H172" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="I172" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="J172" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="11">
+        <v>170</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G173" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="H173" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="I173" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="J173" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="11">
+        <v>171</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="E174" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G174" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="H174" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="I174" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="J174" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="11">
+        <v>172</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="E175" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G175" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="H175" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="I175" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="J175" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="11">
+        <v>173</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="H176" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="I176" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="J176" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="11">
+        <v>174</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="H177" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="I177" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="J177" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="11">
+        <v>175</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="E178" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="H178" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="I178" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="J178" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="11">
+        <v>176</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="E179" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G179" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="H179" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="I179" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="J179" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
